--- a/results/02_taxa_assemblage/LDA_Method/ModelD_AllSites/tables/wilks_importance.xlsx
+++ b/results/02_taxa_assemblage/LDA_Method/ModelD_AllSites/tables/wilks_importance.xlsx
@@ -477,27 +477,27 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.1921112363488744</v>
+        <v>0.1678721998387374</v>
       </c>
       <c r="C2" t="n">
-        <v>6.609081402944433</v>
+        <v>9.280413455092432</v>
       </c>
       <c r="D2" t="n">
-        <v>0.003142127792094218</v>
+        <v>0.0004461965739922524</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>**</t>
+          <t>***</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>-0.7356834053880064</v>
+        <v>-0.5602299537326692</v>
       </c>
       <c r="G2" t="n">
-        <v>1.204156784813054</v>
+        <v>2.23681620712218</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.0931140833443105</v>
+        <v>-0.2764217298386867</v>
       </c>
     </row>
     <row r="3">
@@ -507,27 +507,27 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.04475405644454422</v>
+        <v>0.08582014659489806</v>
       </c>
       <c r="C3" t="n">
-        <v>1.539645508380467</v>
+        <v>4.744361746271183</v>
       </c>
       <c r="D3" t="n">
-        <v>0.2260462702430677</v>
+        <v>0.0137452473124795</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>ns</t>
+          <t>*</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>-0.4052743084779746</v>
+        <v>-0.229869812585279</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2018545877052658</v>
+        <v>-0.5402325139327899</v>
       </c>
       <c r="H3" t="n">
-        <v>0.2820056789396145</v>
+        <v>1.198805681553875</v>
       </c>
     </row>
     <row r="4">
@@ -537,13 +537,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.02097826171893824</v>
+        <v>0.0397977756355542</v>
       </c>
       <c r="C4" t="n">
-        <v>0.72170187453769</v>
+        <v>2.200124933406157</v>
       </c>
       <c r="D4" t="n">
-        <v>0.4917162677515369</v>
+        <v>0.1231085533119194</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -551,13 +551,13 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>0.1808718635098738</v>
+        <v>0.2123423080878606</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.4050874580728825</v>
+        <v>-1.078053542779271</v>
       </c>
       <c r="H4" t="n">
-        <v>0.101642863792215</v>
+        <v>0.3119870334289762</v>
       </c>
     </row>
     <row r="5">
@@ -567,13 +567,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.01698502304599137</v>
+        <v>0.02071989381820033</v>
       </c>
       <c r="C5" t="n">
-        <v>0.5843250091732693</v>
+        <v>1.145449821728858</v>
       </c>
       <c r="D5" t="n">
-        <v>0.5618470372533557</v>
+        <v>0.3275943664967489</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -581,13 +581,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>-0.2255781300325029</v>
+        <v>-0.2002328335930415</v>
       </c>
       <c r="G5" t="n">
-        <v>0.2880783179482601</v>
+        <v>0.6588385853948219</v>
       </c>
       <c r="H5" t="n">
-        <v>0.03005368540500956</v>
+        <v>0.02776705728308901</v>
       </c>
     </row>
     <row r="6">
@@ -597,13 +597,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.01105699906961677</v>
+        <v>0.0188013034165464</v>
       </c>
       <c r="C6" t="n">
-        <v>0.3803869482713172</v>
+        <v>1.039385135643701</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6858741405775476</v>
+        <v>0.3623869094172412</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -611,13 +611,13 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>-0.04016921522538514</v>
+        <v>0.1079907496499209</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.1778983891261464</v>
+        <v>0.1741868339495472</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1708830082179012</v>
+        <v>-0.491539474469347</v>
       </c>
     </row>
   </sheetData>
